--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571962297</v>
+        <v>46157.93110410638</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110410638</v>
+        <v>46157.93178735142</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178735142</v>
+        <v>46157.93403541791</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93403541791</v>
+        <v>46157.93721534518</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93721534518</v>
+        <v>46158.28219512559</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219512559</v>
+        <v>46158.29694356873</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29694356873</v>
+        <v>46158.29818959666</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29818959666</v>
+        <v>46158.33390595559</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33390595559</v>
+        <v>46158.36860330133</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/25. ООО Т2 МОБАЙЛ/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36860330133</v>
+        <v>46158.37291041025</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
